--- a/synthetic/output/anomalies/anomalies.xlsx
+++ b/synthetic/output/anomalies/anomalies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rx_drop,sales_spike,cross_territory</t>
+          <t>sales_spike</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rx_drop,sales_spike,doctor_concentration</t>
+          <t>payout_discrepancy,doctor_concentration,rx_drop</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>payout_discrepancy,doctor_concentration</t>
+          <t>rx_drop,doctor_concentration,payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -517,56 +517,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>doctor_concentration</t>
+          <t>cross_territory,rx_drop</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rx_drop,cross_territory</t>
+          <t>cross_territory</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cross_territory,sales_spike</t>
+          <t>cross_territory,rx_drop</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rx_drop,doctor_concentration,cross_territory</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -605,34 +605,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>doctor_concentration</t>
+          <t>rx_drop,sales_spike</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>payout_discrepancy</t>
+          <t>payout_discrepancy,sales_spike</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -661,34 +661,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sales_spike,doctor_concentration,payout_discrepancy</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,29 +698,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rx_drop,sales_spike</t>
+          <t>doctor_concentration</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cross_territory,payout_discrepancy</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,73 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>doctor_concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>cross_territory,payout_discrepancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rx_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>doctor_concentration,sales_spike</t>
         </is>
       </c>
     </row>

--- a/synthetic/output/anomalies/anomalies.xlsx
+++ b/synthetic/output/anomalies/anomalies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FR0001</t>
+          <t>FR0002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sales_spike</t>
+          <t>sales_spike,doctor_concentration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FR0001</t>
+          <t>FR0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>payout_discrepancy,doctor_concentration,rx_drop</t>
+          <t>payout_discrepancy,sales_spike</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rx_drop,doctor_concentration,payout_discrepancy</t>
+          <t>sales_spike,rx_drop</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,29 +522,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cross_territory,rx_drop</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>cross_territory</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cross_territory,rx_drop</t>
+          <t>cross_territory</t>
         </is>
       </c>
     </row>
@@ -578,39 +578,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>payout_discrepancy</t>
+          <t>doctor_concentration,cross_territory</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rx_drop,sales_spike</t>
+          <t>payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>payout_discrepancy,sales_spike</t>
+          <t>doctor_concentration,cross_territory,payout_discrepancy</t>
         </is>
       </c>
     </row>
@@ -644,95 +644,95 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>doctor_concentration</t>
+          <t>cross_territory,payout_discrepancy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FR0008</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>payout_discrepancy</t>
+          <t>doctor_concentration</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FR0008</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>doctor_concentration</t>
+          <t>cross_territory,doctor_concentration,sales_spike</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FR0008</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>payout_discrepancy</t>
+          <t>payout_discrepancy,sales_spike</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,73 +742,183 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>doctor_concentration</t>
+          <t>cross_territory,rx_drop</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FR0010</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cross_territory,payout_discrepancy</t>
+          <t>cross_territory</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FR0010</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rx_drop</t>
+          <t>doctor_concentration</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FR0010</t>
+          <t>FR0014</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>doctor_concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FR0014</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>P028</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>payout_discrepancy,cross_territory</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FR0022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>payout_discrepancy,doctor_concentration</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FR0022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>rx_drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FR0026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>doctor_concentration,sales_spike</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>doctor_concentration,cross_territory</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FR0028</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cross_territory,doctor_concentration,sales_spike</t>
         </is>
       </c>
     </row>
